--- a/r5-aist-trustworthyai-main/StructureDefinition-automated-decision-flag.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-automated-decision-flag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Indicates whether the AI-generated output was used as part of a solely automated decision-making process within the meaning of GDPR Article 22.</t>
+    <t>Indicates whether the documented AI-supported processing resulted in a decision made solely by automated means.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>79</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-automated-decision-flag.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-automated-decision-flag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-automated-decision-flag.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-automated-decision-flag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-automated-decision-flag.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-automated-decision-flag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Observation</t>
+    <t>element:Provenance</t>
   </si>
   <si>
     <t>ID</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-automated-decision-flag.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-automated-decision-flag.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/StructureDefinition/automated-decision-flag</t>
+    <t>http://example.org/fhir/trust-ai-transparency/StructureDefinition/automated-decision-flag</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:39:53+00:00</t>
+    <t>2026-09-09T11:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
